--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-11T01:14:47.516070</t>
+          <t>2026-06-11T14:32:03.326413</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-11 01:14:48</t>
+          <t>2026-06-11 14:32:03</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-11T14:32:03.326413</t>
+          <t>2026-06-12T13:59:19.140897</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-11 14:32:03</t>
+          <t>2026-06-12 13:59:19</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-12T13:59:19.140897</t>
+          <t>2026-06-13T12:20:33.700255</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-12 13:59:19</t>
+          <t>2026-06-13 12:20:34</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-13T12:20:33.700255</t>
+          <t>2026-06-14T12:58:13.345242</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-13 12:20:34</t>
+          <t>2026-06-14 12:58:13</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -436,22 +436,22 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>uf_valor_anterior</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>uf_fecha_anterior</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>uf_valor_actual</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>uf_fecha_actual</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>uf_valor_anterior</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>uf_fecha_anterior</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -548,43 +548,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mayo 2026</t>
+          <t>Junio 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-14T12:58:13.345242</t>
+          <t>2026-06-15T16:13:55.235916</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Junio 2026</t>
+          <t>Julio 2026</t>
         </is>
       </c>
       <c r="D2" t="n">
+        <v>40820.31</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Al 30 de Junio del 2026:</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>40610.69</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Al 31 de Mayo del 2026:</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>40120.2</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Al 30 de Abril del 2026:</t>
-        </is>
-      </c>
       <c r="H2" t="n">
-        <v>3654962</v>
+        <v>3673828</v>
       </c>
       <c r="I2" t="n">
-        <v>2407212</v>
+        <v>2436641</v>
       </c>
       <c r="J2" t="n">
-        <v>5490565</v>
+        <v>5518906</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -597,13 +597,13 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>2030535</v>
+        <v>2041016</v>
       </c>
       <c r="N2" t="n">
-        <v>24366414</v>
+        <v>24492186</v>
       </c>
       <c r="O2" t="n">
-        <v>36549621</v>
+        <v>36738279</v>
       </c>
       <c r="P2" t="n">
         <v>539000</v>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-14 12:58:13</t>
+          <t>2026-06-15 16:13:55</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-15T16:13:55.235916</t>
+          <t>2026-06-16T15:49:48.487034</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-15 16:13:55</t>
+          <t>2026-06-16 15:49:48</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16T15:49:48.487034</t>
+          <t>2026-06-17T14:24:36.076773</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16 15:49:48</t>
+          <t>2026-06-17 14:24:36</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-17T14:24:36.076773</t>
+          <t>2026-06-18T13:57:52.144305</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-17 14:24:36</t>
+          <t>2026-06-18 13:57:52</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-18T13:57:52.144305</t>
+          <t>2026-06-19T13:58:57.171680</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-18 13:57:52</t>
+          <t>2026-06-19 13:58:57</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-19T13:58:57.171680</t>
+          <t>2026-06-20T12:24:21.879351</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-19 13:58:57</t>
+          <t>2026-06-20 12:24:22</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-20T12:24:21.879351</t>
+          <t>2026-06-21T13:02:01.990535</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-20 12:24:22</t>
+          <t>2026-06-21 13:02:02</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-21T13:02:01.990535</t>
+          <t>2026-06-22T15:48:16.866169</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-21 13:02:02</t>
+          <t>2026-06-22 15:48:17</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-22T15:48:16.866169</t>
+          <t>2026-06-23T13:37:22.889790</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -606,16 +606,16 @@
         <v>36738279</v>
       </c>
       <c r="P2" t="n">
-        <v>539000</v>
+        <v>553553</v>
       </c>
       <c r="Q2" t="n">
-        <v>402082</v>
+        <v>412938</v>
       </c>
       <c r="R2" t="n">
-        <v>539000</v>
+        <v>553553</v>
       </c>
       <c r="S2" t="n">
-        <v>347434</v>
+        <v>356815</v>
       </c>
       <c r="T2" t="n">
         <v>0.9</v>
@@ -640,7 +640,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[{'tramo': '1 (A)', 'monto': '$ 22.007', 'requisito_renta': 'Renta &lt; ó = $ 631.976'}, {'tramo': '2 (B)', 'monto': '$ 13.505', 'requisito_renta': 'Renta &gt; $ 631.976 &lt; = $ 923.067'}, {'tramo': '3 (C)', 'monto': '$ 4.267', 'requisito_renta': 'Renta &gt; $ 923.067 &lt; = $ 1.439.668'}, {'tramo': '4 (D)', 'monto': '–', 'requisito_renta': 'Renta &gt; $ 1.439.668'}]</t>
+          <t>[{'tramo': '1 (A)', 'monto': '$ 22.601', 'requisito_renta': 'Renta &lt; ó = $ 649.039'}, {'tramo': '2 (B)', 'monto': '$ 13.870', 'requisito_renta': 'Renta &gt; $ 649.039 &lt; = $ 947.990'}, {'tramo': '3 (C)', 'monto': '$ 4.382', 'requisito_renta': 'Renta &gt; $ 947.990 &lt; = $ 1.478.539'}, {'tramo': '4 (D)', 'monto': '–', 'requisito_renta': 'Renta &gt; $ 1.478.539'}]</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-22 15:48:17</t>
+          <t>2026-06-23 13:37:24</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-23T13:37:22.889790</t>
+          <t>2026-06-24T13:12:29.812678</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-23 13:37:24</t>
+          <t>2026-06-24 13:12:30</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-24T13:12:29.812678</t>
+          <t>2026-06-25T13:12:07.979456</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-24 13:12:30</t>
+          <t>2026-06-25 13:12:08</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-25T13:12:07.979456</t>
+          <t>2026-06-26T13:04:25.639208</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-25 13:12:08</t>
+          <t>2026-06-26 13:04:26</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-26T13:04:25.639208</t>
+          <t>2026-06-27T12:05:29.574243</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-26 13:04:26</t>
+          <t>2026-06-27 12:05:29</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-27T12:05:29.574243</t>
+          <t>2026-06-28T12:12:57.271766</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-27 12:05:29</t>
+          <t>2026-06-28 12:12:57</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-28T12:12:57.271766</t>
+          <t>2026-06-29T14:42:50.484606</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-28 12:12:57</t>
+          <t>2026-06-29 14:42:50</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-29T14:42:50.484606</t>
+          <t>2026-06-30T13:04:53.776758</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-29 14:42:50</t>
+          <t>2026-06-30 13:04:54</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-30T13:04:53.776758</t>
+          <t>2026-07-01T13:32:07.521234</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-30 13:04:54</t>
+          <t>2026-07-01 13:32:07</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-01T13:32:07.521234</t>
+          <t>2026-07-02T12:53:50.484909</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-01 13:32:07</t>
+          <t>2026-07-02 12:53:50</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-02T12:53:50.484909</t>
+          <t>2026-07-03T12:52:17.504158</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-02 12:53:50</t>
+          <t>2026-07-03 12:52:17</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-03T12:52:17.504158</t>
+          <t>2026-07-04T12:01:46.753326</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-03 12:52:17</t>
+          <t>2026-07-04 12:01:47</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-04T12:01:46.753326</t>
+          <t>2026-07-05T12:09:57.070210</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-04 12:01:47</t>
+          <t>2026-07-05 12:09:57</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-05T12:09:57.070210</t>
+          <t>2026-07-06T14:22:19.083036</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-05 12:09:57</t>
+          <t>2026-07-06 14:22:19</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-06T14:22:19.083036</t>
+          <t>2026-07-07T13:12:28.947723</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-06 14:22:19</t>
+          <t>2026-07-07 13:12:29</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-07T13:12:28.947723</t>
+          <t>2026-07-08T12:14:44.379737</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-07 13:12:29</t>
+          <t>2026-07-08 12:14:44</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-08T12:14:44.379737</t>
+          <t>2026-07-09T13:44:25.250227</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -896,10 +896,26 @@
           <t>858.072</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>112,35</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2,8</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4,3</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -928,8 +944,16 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>71.649</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>859.788</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
@@ -1021,7 +1045,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-08 12:14:44</t>
+          <t>2026-07-09 13:44:25</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-09T13:44:25.250227</t>
+          <t>2026-07-10T13:04:53.830314</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-09 13:44:25</t>
+          <t>2026-07-10 13:04:54</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-10T13:04:53.830314</t>
+          <t>2026-07-11T11:45:21.397552</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-10 13:04:54</t>
+          <t>2026-07-11 11:45:21</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-11T11:45:21.397552</t>
+          <t>2026-07-12T11:52:49.195998</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-11 11:45:21</t>
+          <t>2026-07-12 11:52:49</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,100 +446,90 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>uf_valor_actual</t>
+          <t>renta_tope_afp</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>uf_fecha_actual</t>
+          <t>renta_tope_ips</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>renta_tope_afp</t>
+          <t>renta_tope_seguro_cesantia</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>renta_tope_ips</t>
+          <t>afp_tasas</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>renta_tope_seguro_cesantia</t>
+          <t>seguro_cesantia</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>afp_tasas</t>
+          <t>apv_tope_mensual</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>seguro_cesantia</t>
+          <t>apv_tope_anual</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>apv_tope_mensual</t>
+          <t>deposito_convenido_tope_anual</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>apv_tope_anual</t>
+          <t>renta_minima_dependientes</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>deposito_convenido_tope_anual</t>
+          <t>renta_minima_menores_mayores</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>renta_minima_dependientes</t>
+          <t>renta_minima_casa_particular</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>renta_minima_menores_mayores</t>
+          <t>renta_minima_no_remuneracional</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>renta_minima_casa_particular</t>
+          <t>seguro_social</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>renta_minima_no_remuneracional</t>
+          <t>sis_tasa</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>seguro_social</t>
+          <t>salud_ccaf</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>sis_tasa</t>
+          <t>salud_fonasa</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>salud_ccaf</t>
+          <t>trabajos_pesados</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
-        <is>
-          <t>salud_fonasa</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>trabajos_pesados</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
         <is>
           <t>asignacion_familiar</t>
         </is>
@@ -548,17 +538,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Junio 2026</t>
+          <t>Julio 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12T11:52:49.195998</t>
+          <t>2026-07-14T12:06:10.545153</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Julio 2026</t>
+          <t>Agosto 2026</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -570,75 +560,67 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>40610.69</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Al 31 de Mayo del 2026:</t>
-        </is>
+        <v>3676031</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2449219</v>
       </c>
       <c r="H2" t="n">
-        <v>3673828</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2436641</v>
-      </c>
-      <c r="J2" t="n">
-        <v>5518906</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>[{'nombre': 'Cuprum', 'trabajador': '11,44%', 'empleador': '0,1%', 'total_dependiente': '11,54%', 'total_independiente': '13,06%'}, {'nombre': 'Habitat', 'trabajador': '11,27%', 'empleador': '0,1%', 'total_dependiente': '11,37%', 'total_independiente': '12,89%'}, {'nombre': 'PlanVital', 'trabajador': '11,16%', 'empleador': '0,1%', 'total_dependiente': '11,26%', 'total_independiente': '12,78%'}, {'nombre': 'ProVida', 'trabajador': '11,45%', 'empleador': '0,1%', 'total_dependiente': '11,55%', 'total_independiente': '13,07%'}, {'nombre': 'Modelo', 'trabajador': '10,58%', 'empleador': '0,1%', 'total_dependiente': '10,68%', 'total_independiente': '12,20%'}, {'nombre': 'Uno', 'trabajador': '10,46%', 'empleador': '0,1%', 'total_dependiente': '10,56%', 'total_independiente': '12,08%'}]</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+        <v>5522216</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>[{'nombre': 'Cuprum', 'trabajador': '11,44%', 'empleador': '0,1%', 'total_dependiente': '11,54%', 'total_independiente': '13,44%'}, {'nombre': 'Habitat', 'trabajador': '11,27%', 'empleador': '0,1%', 'total_dependiente': '11,37%', 'total_independiente': '13,27%'}, {'nombre': 'PlanVital', 'trabajador': '11,16%', 'empleador': '0,1%', 'total_dependiente': '11,26%', 'total_independiente': '13,16%'}, {'nombre': 'ProVida', 'trabajador': '11,45%', 'empleador': '0,1%', 'total_dependiente': '11,55%', 'total_independiente': '13,45%'}, {'nombre': 'Modelo', 'trabajador': '10,58%', 'empleador': '0,1%', 'total_dependiente': '10,68%', 'total_independiente': '12,58%'}, {'nombre': 'Uno', 'trabajador': '10,46%', 'empleador': '0,1%', 'total_dependiente': '10,56%', 'total_independiente': '12,46%'}]</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>[{'contrato': 'Plazo Indefinido', 'empleador': '2,4% R.I.', 'trabajador': '0,6% R.I.'}, {'contrato': 'Plazo Fijo', 'empleador': '3,0% R.I.', 'trabajador': '–'}, {'contrato': 'Plazo Indefinido 11 años o más (*)', 'empleador': '0,8% R.I.', 'trabajador': '–'}, {'contrato': 'Trabajador de Casa Particular (**)', 'empleador': '3,0% R.I.', 'trabajador': '–'}]</t>
         </is>
       </c>
+      <c r="K2" t="n">
+        <v>2042240</v>
+      </c>
+      <c r="L2" t="n">
+        <v>24506874</v>
+      </c>
       <c r="M2" t="n">
-        <v>2041016</v>
+        <v>36760311</v>
       </c>
       <c r="N2" t="n">
-        <v>24492186</v>
+        <v>553553</v>
       </c>
       <c r="O2" t="n">
-        <v>36738279</v>
+        <v>412938</v>
       </c>
       <c r="P2" t="n">
         <v>553553</v>
       </c>
       <c r="Q2" t="n">
-        <v>412938</v>
+        <v>356815</v>
       </c>
       <c r="R2" t="n">
-        <v>553553</v>
+        <v>0.9</v>
       </c>
       <c r="S2" t="n">
-        <v>356815</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.62</v>
+        <v>2</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>4,2% R.I.</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2,8% R.I.</t>
+        </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>4,2% R.I.</t>
+          <t>[{'tipo': 'Trabajo pesado', 'porcentaje': '4%', 'empleador': '2% R.I.', 'trabajador': '2% R.I.'}, {'tipo': 'Trabajo menos pesado', 'porcentaje': '2%', 'empleador': '1% R.I.', 'trabajador': '1% R.I.'}]</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
-        <is>
-          <t>2,8% R.I.</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>[{'tipo': 'Trabajo pesado', 'porcentaje': '4%', 'empleador': '2% R.I.', 'trabajador': '2% R.I.'}, {'tipo': 'Trabajo menos pesado', 'porcentaje': '2%', 'empleador': '1% R.I.', 'trabajador': '1% R.I.'}]</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
         <is>
           <t>[{'tramo': '1 (A)', 'monto': '$ 22.601', 'requisito_renta': 'Renta &lt; ó = $ 649.039'}, {'tramo': '2 (B)', 'monto': '$ 13.870', 'requisito_renta': 'Renta &gt; $ 649.039 &lt; = $ 947.990'}, {'tramo': '3 (C)', 'monto': '$ 4.382', 'requisito_renta': 'Renta &gt; $ 947.990 &lt; = $ 1.478.539'}, {'tramo': '4 (D)', 'monto': '–', 'requisito_renta': 'Renta &gt; $ 1.478.539'}]</t>
         </is>
@@ -1045,7 +1027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12 11:52:49</t>
+          <t>2026-07-14 12:06:13</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-14T12:06:10.545153</t>
+          <t>2026-07-15T12:10:02.066974</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-14 12:06:13</t>
+          <t>2026-07-15 12:10:02</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-15T12:10:02.066974</t>
+          <t>2026-07-16T12:14:45.409899</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-15 12:10:02</t>
+          <t>2026-07-16 12:14:45</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-16T12:14:45.409899</t>
+          <t>2026-07-17T12:03:03.485129</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-16 12:14:45</t>
+          <t>2026-07-17 12:03:03</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-17T12:03:03.485129</t>
+          <t>2026-07-18T11:45:20.006191</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-17 12:03:03</t>
+          <t>2026-07-18 11:45:20</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-18T11:45:20.006191</t>
+          <t>2026-07-19T11:49:05.722398</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-18 11:45:20</t>
+          <t>2026-07-19 11:49:06</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-19T11:49:05.722398</t>
+          <t>2026-07-20T13:01:10.980546</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-19 11:49:06</t>
+          <t>2026-07-20 13:01:11</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-20T13:01:10.980546</t>
+          <t>2026-07-21T12:19:59.405462</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-20 13:01:11</t>
+          <t>2026-07-21 12:19:59</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-21T12:19:59.405462</t>
+          <t>2026-07-22T12:22:45.808971</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-21 12:19:59</t>
+          <t>2026-07-22 12:22:46</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-22T12:22:45.808971</t>
+          <t>2026-07-23T12:19:42.566114</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-22 12:22:46</t>
+          <t>2026-07-23 12:19:42</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-23T12:19:42.566114</t>
+          <t>2026-07-24T12:13:59.624059</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-23 12:19:42</t>
+          <t>2026-07-24 12:13:59</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-24T12:13:59.624059</t>
+          <t>2026-07-25T11:57:11.179468</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-24 12:13:59</t>
+          <t>2026-07-25 11:57:11</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-25T11:57:11.179468</t>
+          <t>2026-07-26T11:55:47.678662</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-25 11:57:11</t>
+          <t>2026-07-26 11:55:48</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-26T11:55:47.678662</t>
+          <t>2026-07-27T13:32:51.608041</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-26 11:55:48</t>
+          <t>2026-07-27 13:32:51</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-27T13:32:51.608041</t>
+          <t>2026-07-28T12:48:51.509843</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-27 13:32:51</t>
+          <t>2026-07-28 12:48:51</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-28T12:48:51.509843</t>
+          <t>2026-07-29T12:56:02.433549</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-28 12:48:51</t>
+          <t>2026-07-29 12:56:02</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-29T12:56:02.433549</t>
+          <t>2026-07-30T12:24:01.900466</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-29 12:56:02</t>
+          <t>2026-07-30 12:24:02</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-30T12:24:01.900466</t>
+          <t>2026-07-31T12:51:21.482259</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-30 12:24:02</t>
+          <t>2026-07-31 12:51:21</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31T12:51:21.482259</t>
+          <t>2026-08-01T11:56:53.636783</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31 12:51:21</t>
+          <t>2026-08-01 11:56:54</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01T11:56:53.636783</t>
+          <t>2026-08-02T11:54:54.490887</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01 11:56:54</t>
+          <t>2026-08-02 11:54:54</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02T11:54:54.490887</t>
+          <t>2026-08-03T13:33:14.006455</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02 11:54:54</t>
+          <t>2026-08-03 13:33:14</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-03T13:33:14.006455</t>
+          <t>2026-08-04T12:53:30.936188</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-03 13:33:14</t>
+          <t>2026-08-04 12:53:31</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-04T12:53:30.936188</t>
+          <t>2026-08-05T12:48:11.454475</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-04 12:53:31</t>
+          <t>2026-08-05 12:48:12</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-05T12:48:11.454475</t>
+          <t>2026-08-06T12:51:27.517311</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-05 12:48:12</t>
+          <t>2026-08-06 12:51:27</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-06T12:51:27.517311</t>
+          <t>2026-08-07T11:38:36.116626</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-06 12:51:27</t>
+          <t>2026-08-07 11:38:36</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-07T11:38:36.116626</t>
+          <t>2026-08-08T11:20:29.188529</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -915,10 +915,26 @@
           <t>859.788</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>112,45</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0,1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2,9</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -947,8 +963,16 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>71.721</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>860.652</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
@@ -1027,7 +1051,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-07 11:38:36</t>
+          <t>2026-08-08 11:20:29</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08T11:20:29.188529</t>
+          <t>2026-08-09T11:21:09.561738</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08 11:20:29</t>
+          <t>2026-08-09 11:21:09</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09T11:21:09.561738</t>
+          <t>2026-08-10T11:41:44.207350</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09 11:21:09</t>
+          <t>2026-08-10 11:41:44</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-10T11:41:44.207350</t>
+          <t>2026-08-11T11:37:20.314296</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-10 11:41:44</t>
+          <t>2026-08-11 11:37:20</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-11T11:37:20.314296</t>
+          <t>2026-08-12T11:39:26.948310</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-11 11:37:20</t>
+          <t>2026-08-12 11:39:27</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-12T11:39:26.948310</t>
+          <t>2026-08-13T11:39:57.508933</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-12 11:39:27</t>
+          <t>2026-08-13 11:39:57</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,25 +511,20 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>sis_tasa</t>
+          <t>salud_ccaf</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>salud_ccaf</t>
+          <t>salud_fonasa</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>salud_fonasa</t>
+          <t>trabajos_pesados</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
-        <is>
-          <t>trabajos_pesados</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
         <is>
           <t>asignacion_familiar</t>
         </is>
@@ -538,39 +533,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Julio 2026</t>
+          <t>Agosto 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-13T11:39:57.508933</t>
+          <t>2026-08-14T11:37:26.626829</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Septiembre 2026</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>40820.31</v>
+        <v>40844.79</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al 30 de Junio del 2026:</t>
+          <t>Al 31 de Julio del 2026:</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3676031</v>
+        <v>3678639</v>
       </c>
       <c r="G2" t="n">
-        <v>2449219</v>
+        <v>2450687</v>
       </c>
       <c r="H2" t="n">
-        <v>5522216</v>
+        <v>5526134</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[{'nombre': 'Cuprum', 'trabajador': '11,44%', 'empleador': '0,1%', 'total_dependiente': '11,54%', 'total_independiente': '13,44%'}, {'nombre': 'Habitat', 'trabajador': '11,27%', 'empleador': '0,1%', 'total_dependiente': '11,37%', 'total_independiente': '13,27%'}, {'nombre': 'PlanVital', 'trabajador': '11,16%', 'empleador': '0,1%', 'total_dependiente': '11,26%', 'total_independiente': '13,16%'}, {'nombre': 'ProVida', 'trabajador': '11,45%', 'empleador': '0,1%', 'total_dependiente': '11,55%', 'total_independiente': '13,45%'}, {'nombre': 'Modelo', 'trabajador': '10,58%', 'empleador': '0,1%', 'total_dependiente': '10,68%', 'total_independiente': '12,58%'}, {'nombre': 'Uno', 'trabajador': '10,46%', 'empleador': '0,1%', 'total_dependiente': '10,56%', 'total_independiente': '12,46%'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -579,13 +574,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2042240</v>
+        <v>2043689</v>
       </c>
       <c r="L2" t="n">
-        <v>24506874</v>
+        <v>24524262</v>
       </c>
       <c r="M2" t="n">
-        <v>36760311</v>
+        <v>36786393</v>
       </c>
       <c r="N2" t="n">
         <v>553553</v>
@@ -600,27 +595,24 @@
         <v>356815</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2</v>
+        <v>0.5</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>4,2% R.I.</t>
+        </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>4,2% R.I.</t>
+          <t>2,8% R.I.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2,8% R.I.</t>
+          <t>[{'tipo': 'Trabajo pesado', 'porcentaje': '4%', 'empleador': '2% R.I.', 'trabajador': '2% R.I.'}, {'tipo': 'Trabajo menos pesado', 'porcentaje': '2%', 'empleador': '1% R.I.', 'trabajador': '1% R.I.'}]</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
-        <is>
-          <t>[{'tipo': 'Trabajo pesado', 'porcentaje': '4%', 'empleador': '2% R.I.', 'trabajador': '2% R.I.'}, {'tipo': 'Trabajo menos pesado', 'porcentaje': '2%', 'empleador': '1% R.I.', 'trabajador': '1% R.I.'}]</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
         <is>
           <t>[{'tramo': '1 (A)', 'monto': '$ 22.601', 'requisito_renta': 'Renta &lt; ó = $ 649.039'}, {'tramo': '2 (B)', 'monto': '$ 13.870', 'requisito_renta': 'Renta &gt; $ 649.039 &lt; = $ 947.990'}, {'tramo': '3 (C)', 'monto': '$ 4.382', 'requisito_renta': 'Renta &gt; $ 947.990 &lt; = $ 1.478.539'}, {'tramo': '4 (D)', 'monto': '–', 'requisito_renta': 'Renta &gt; $ 1.478.539'}]</t>
         </is>
@@ -1051,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-13 11:39:57</t>
+          <t>2026-08-14 11:37:28</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-14T11:37:26.626829</t>
+          <t>2026-08-15T11:11:41.032136</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-14 11:37:28</t>
+          <t>2026-08-15 11:11:41</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15T11:11:41.032136</t>
+          <t>2026-08-16T11:11:43.726886</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15 11:11:41</t>
+          <t>2026-08-16 11:11:44</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16T11:11:43.726886</t>
+          <t>2026-08-17T11:17:01.692175</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16 11:11:44</t>
+          <t>2026-08-17 11:17:02</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-17T11:17:01.692175</t>
+          <t>2026-08-18T11:16:43.262724</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-17 11:17:02</t>
+          <t>2026-08-18 11:16:43</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-18T11:16:43.262724</t>
+          <t>2026-08-19T11:16:48.574107</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -595,7 +595,7 @@
         <v>356815</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:16:43</t>
+          <t>2026-08-19 11:16:50</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-19T11:16:48.574107</t>
+          <t>2026-08-20T11:18:32.852790</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:50</t>
+          <t>2026-08-20 11:18:33</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-20T11:18:32.852790</t>
+          <t>2026-08-21T11:17:51.867086</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-20 11:18:33</t>
+          <t>2026-08-21 11:17:52</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21T11:17:51.867086</t>
+          <t>2026-08-22T11:12:56.255113</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 11:17:52</t>
+          <t>2026-08-22 11:12:56</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-22T11:12:56.255113</t>
+          <t>2026-08-23T11:12:46.092634</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-22 11:12:56</t>
+          <t>2026-08-23 11:12:46</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-23T11:12:46.092634</t>
+          <t>2026-08-24T11:18:41.177456</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-23 11:12:46</t>
+          <t>2026-08-24 11:18:41</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24T11:18:41.177456</t>
+          <t>2026-08-25T11:18:29.295228</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 11:18:41</t>
+          <t>2026-08-25 11:18:29</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25T11:18:29.295228</t>
+          <t>2026-08-26T11:20:20.600705</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25 11:18:29</t>
+          <t>2026-08-26 11:20:20</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26T11:20:20.600705</t>
+          <t>2026-08-27T20:51:52.524616</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:20</t>
+          <t>2026-08-27 20:51:52</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27T20:51:52.524616</t>
+          <t>2026-08-28T21:17:11.911401</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:52</t>
+          <t>2026-08-28 21:17:12</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28T21:17:11.911401</t>
+          <t>2026-08-29T15:23:16.147041</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:12</t>
+          <t>2026-08-29 15:23:16</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-29T15:23:16.147041</t>
+          <t>2026-08-30T15:07:14.494346</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-29 15:23:16</t>
+          <t>2026-08-30 15:07:14</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-30T15:07:14.494346</t>
+          <t>2026-08-31T17:46:19.202417</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:14</t>
+          <t>2026-08-31 17:46:19</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31T17:46:19.202417</t>
+          <t>2026-09-01T15:19:32.709611</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:19</t>
+          <t>2026-09-01 15:19:32</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01T15:19:32.709611</t>
+          <t>2026-09-02T14:49:26.126135</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 15:19:32</t>
+          <t>2026-09-02 14:49:26</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02T14:49:26.126135</t>
+          <t>2026-09-03T14:49:21.630069</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 14:49:26</t>
+          <t>2026-09-03 14:49:22</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03T14:49:21.630069</t>
+          <t>2026-09-04T14:38:06.471922</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:22</t>
+          <t>2026-09-04 14:38:06</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-04T14:38:06.471922</t>
+          <t>2026-09-05T13:37:06.396586</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-04 14:38:06</t>
+          <t>2026-09-05 13:37:06</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05T13:37:06.396586</t>
+          <t>2026-09-06T13:51:08.763899</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05 13:37:06</t>
+          <t>2026-09-06 13:51:08</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06T13:51:08.763899</t>
+          <t>2026-09-07T16:12:59.639687</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:08</t>
+          <t>2026-09-07 16:12:59</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07T16:12:59.639687</t>
+          <t>2026-09-08T14:49:49.480180</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:59</t>
+          <t>2026-09-08 14:49:49</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-08T14:49:49.480180</t>
+          <t>2026-09-09T14:55:30.847481</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -944,10 +944,26 @@
           <t>859.788</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>113,15</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0,6</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>3,6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4,1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -976,8 +992,16 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>72.151</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>865.812</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -1043,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:49</t>
+          <t>2026-09-09 14:55:31</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09T14:55:30.847481</t>
+          <t>2026-09-10T14:42:20.645037</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 14:55:31</t>
+          <t>2026-09-10 14:42:20</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-10T14:42:20.645037</t>
+          <t>2026-09-11T14:43:37.834602</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:20</t>
+          <t>2026-09-11 14:43:38</t>
         </is>
       </c>
     </row>

--- a/data/indicadores_2026.xlsx
+++ b/data/indicadores_2026.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-11T14:43:37.834602</t>
+          <t>2026-09-12T13:48:53.140550</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-11 14:43:38</t>
+          <t>2026-09-12 13:48:54</t>
         </is>
       </c>
     </row>
